--- a/02_Data_Dictionary.xlsx
+++ b/02_Data_Dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/59ed6f6b54feccf0/Desktop/DataAnalysis Portifolio/Banking Operations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{A89CC4EA-D9B9-4F85-9C38-F814125A63D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4637B534-ABC0-4930-8A1A-A2B3F21A0616}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{A89CC4EA-D9B9-4F85-9C38-F814125A63D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1868AD7-72DB-456C-8505-5561ED2A32B5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{321666E2-A9CD-4FE1-A4BC-62E1670B41A7}"/>
   </bookViews>
@@ -116,18 +116,9 @@
     <t>Central, Eastern, Northern, Western</t>
   </si>
   <si>
-    <t>Analyst</t>
-  </si>
-  <si>
-    <t>Analyst assigned to the case</t>
-  </si>
-  <si>
     <t>Lisa N.</t>
   </si>
   <si>
-    <t>List of analysts</t>
-  </si>
-  <si>
     <t>CustomerType</t>
   </si>
   <si>
@@ -210,6 +201,15 @@
   </si>
   <si>
     <t>Indicates whether the case was escalated beyond the assigned analyst or team.</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>Employee assigned to the case</t>
+  </si>
+  <si>
+    <t>List of employees</t>
   </si>
 </sst>
 </file>
@@ -742,143 +742,143 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
         <v>29</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="18:18" x14ac:dyDescent="0.25">
       <c r="R17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
